--- a/E-commerce/Data/ActiTimeTestData.xlsx
+++ b/E-commerce/Data/ActiTimeTestData.xlsx
@@ -1,18 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26227"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{8015F9E2-2E03-4F6F-BE56-2FD9BCD104C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{1B08310B-4C02-41FD-A2F4-31F081D929CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Validcreads" sheetId="1" r:id="rId1"/>
     <sheet name="InValidcreads" sheetId="2" r:id="rId2"/>
+    <sheet name="UserImfromations" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
-  <oleSize ref="A1:J9"/>
+  <oleSize ref="A1:H3"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -22,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="28">
   <si>
     <t>username</t>
   </si>
@@ -33,47 +34,86 @@
     <t>admin</t>
   </si>
   <si>
-    <t>ad min</t>
-  </si>
-  <si>
-    <t>admin@34</t>
-  </si>
-  <si>
-    <t>ma@ger</t>
+    <t>status</t>
+  </si>
+  <si>
+    <t>admin123</t>
   </si>
   <si>
     <t>Admin</t>
   </si>
   <si>
-    <t>admin123</t>
-  </si>
-  <si>
-    <t>Username</t>
-  </si>
-  <si>
-    <t>Adman</t>
-  </si>
-  <si>
-    <t>admin1</t>
-  </si>
-  <si>
-    <t>admin23</t>
-  </si>
-  <si>
-    <t>admio</t>
-  </si>
-  <si>
-    <t>Addd</t>
-  </si>
-  <si>
-    <t>adddff</t>
+    <t>admin12</t>
+  </si>
+  <si>
+    <t>Adamin12</t>
+  </si>
+  <si>
+    <t>Ad min</t>
+  </si>
+  <si>
+    <t>adm in123</t>
+  </si>
+  <si>
+    <t>Admin@34</t>
+  </si>
+  <si>
+    <t>admin@123</t>
+  </si>
+  <si>
+    <t>LastName</t>
+  </si>
+  <si>
+    <t>FistName</t>
+  </si>
+  <si>
+    <t>MiddleName</t>
+  </si>
+  <si>
+    <t>Employee Id</t>
+  </si>
+  <si>
+    <t>Maruti</t>
+  </si>
+  <si>
+    <t>Bharat</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Kolavale</t>
+  </si>
+  <si>
+    <t>Samir</t>
+  </si>
+  <si>
+    <t>nagantha</t>
+  </si>
+  <si>
+    <t>Kore</t>
+  </si>
+  <si>
+    <t>Santosh</t>
+  </si>
+  <si>
+    <t>Hari</t>
+  </si>
+  <si>
+    <t>Kadam</t>
+  </si>
+  <si>
+    <t>Ram</t>
+  </si>
+  <si>
+    <t>Harish</t>
+  </si>
+  <si>
+    <t>Pawar</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -90,9 +130,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -106,7 +152,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -114,16 +160,38 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -405,7 +473,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -418,21 +486,16 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -443,7 +506,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1706B3E-5694-490A-A3AA-AA7124E50574}">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.88671875" customWidth="1"/>
@@ -451,79 +514,71 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B1" s="3" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>7</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="B2" s="1"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="1"/>
+        <v>7</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -534,4 +589,92 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA5F9962-3B25-4185-8B1B-9AC14D8F6189}">
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13" style="3" customWidth="1"/>
+    <col min="5" max="16384" width="8.88671875" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="5">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/E-commerce/Data/ActiTimeTestData.xlsx
+++ b/E-commerce/Data/ActiTimeTestData.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26227"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{1B08310B-4C02-41FD-A2F4-31F081D929CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{8EB43EBF-967B-43F7-9BF1-C714F9F33562}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Validcreads" sheetId="1" r:id="rId1"/>
@@ -13,7 +13,7 @@
     <sheet name="UserImfromations" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
-  <oleSize ref="A1:H3"/>
+  <oleSize ref="A1:G3"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="29">
   <si>
     <t>username</t>
   </si>
@@ -107,6 +107,9 @@
   </si>
   <si>
     <t>Pawar</t>
+  </si>
+  <si>
+    <t>A</t>
   </si>
 </sst>
 </file>
@@ -473,7 +476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -498,6 +501,7 @@
         <v>4</v>
       </c>
     </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -525,7 +529,9 @@
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="1"/>
+      <c r="B2" s="1" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>

--- a/E-commerce/Data/ActiTimeTestData.xlsx
+++ b/E-commerce/Data/ActiTimeTestData.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26327"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{8EB43EBF-967B-43F7-9BF1-C714F9F33562}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{8C731A01-744C-41CB-A2CB-A972BBC45EE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Validcreads" sheetId="1" r:id="rId1"/>
@@ -13,7 +13,7 @@
     <sheet name="UserImfromations" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
-  <oleSize ref="A1:G3"/>
+  <oleSize ref="A1:F6"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
